--- a/Team-Data/2008-09/3-30-2008-09.xlsx
+++ b/Team-Data/2008-09/3-30-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>2</v>
       </c>
       <c r="AD2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
@@ -775,13 +842,13 @@
         <v>24</v>
       </c>
       <c r="AP2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AQ2" t="n">
         <v>29</v>
       </c>
       <c r="AR2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS2" t="n">
         <v>20</v>
@@ -790,16 +857,16 @@
         <v>21</v>
       </c>
       <c r="AU2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW2" t="n">
         <v>11</v>
       </c>
       <c r="AX2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY2" t="n">
         <v>7</v>
@@ -808,10 +875,10 @@
         <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC2" t="n">
         <v>11</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-30-2008-09</t>
+          <t>2009-03-30</t>
         </is>
       </c>
     </row>
@@ -843,70 +910,70 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E3" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F3" t="n">
         <v>19</v>
       </c>
       <c r="G3" t="n">
-        <v>0.743</v>
+        <v>0.747</v>
       </c>
       <c r="H3" t="n">
         <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J3" t="n">
-        <v>77.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="K3" t="n">
         <v>0.485</v>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M3" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="N3" t="n">
-        <v>0.394</v>
+        <v>0.392</v>
       </c>
       <c r="O3" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="P3" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.771</v>
+        <v>0.768</v>
       </c>
       <c r="R3" t="n">
         <v>10.6</v>
       </c>
       <c r="S3" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T3" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="U3" t="n">
         <v>22.7</v>
       </c>
       <c r="V3" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="W3" t="n">
         <v>7.6</v>
       </c>
       <c r="X3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y3" t="n">
         <v>4.7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>4.8</v>
       </c>
       <c r="Z3" t="n">
         <v>23.2</v>
@@ -915,13 +982,13 @@
         <v>22.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.9</v>
+        <v>100.8</v>
       </c>
       <c r="AC3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
         <v>3</v>
@@ -933,7 +1000,7 @@
         <v>4</v>
       </c>
       <c r="AH3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AI3" t="n">
         <v>9</v>
@@ -945,7 +1012,7 @@
         <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM3" t="n">
         <v>21</v>
@@ -954,13 +1021,13 @@
         <v>1</v>
       </c>
       <c r="AO3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AR3" t="n">
         <v>21</v>
@@ -975,13 +1042,13 @@
         <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AY3" t="n">
         <v>14</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-30-2008-09</t>
+          <t>2009-03-30</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-0.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
         <v>18</v>
@@ -1115,7 +1182,7 @@
         <v>18</v>
       </c>
       <c r="AH4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI4" t="n">
         <v>29</v>
@@ -1145,10 +1212,10 @@
         <v>27</v>
       </c>
       <c r="AR4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT4" t="n">
         <v>27</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-30-2008-09</t>
+          <t>2009-03-30</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F5" t="n">
         <v>39</v>
       </c>
       <c r="G5" t="n">
-        <v>0.473</v>
+        <v>0.48</v>
       </c>
       <c r="H5" t="n">
         <v>48.7</v>
@@ -1225,40 +1292,40 @@
         <v>38.1</v>
       </c>
       <c r="J5" t="n">
-        <v>83.7</v>
+        <v>83.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L5" t="n">
         <v>6</v>
       </c>
       <c r="M5" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0.382</v>
+        <v>0.383</v>
       </c>
       <c r="O5" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="P5" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.793</v>
+        <v>0.792</v>
       </c>
       <c r="R5" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S5" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T5" t="n">
         <v>42.4</v>
       </c>
       <c r="U5" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V5" t="n">
         <v>14.8</v>
@@ -1270,25 +1337,25 @@
         <v>5.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z5" t="n">
         <v>21.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB5" t="n">
         <v>101.9</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.9</v>
+        <v>-0.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF5" t="n">
         <v>17</v>
@@ -1318,10 +1385,10 @@
         <v>5</v>
       </c>
       <c r="AO5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AP5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AQ5" t="n">
         <v>7</v>
@@ -1339,22 +1406,22 @@
         <v>15</v>
       </c>
       <c r="AV5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AX5" t="n">
         <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AZ5" t="n">
         <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BB5" t="n">
         <v>9</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-30-2008-09</t>
+          <t>2009-03-30</t>
         </is>
       </c>
     </row>
@@ -1389,46 +1456,46 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E6" t="n">
         <v>60</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>0.833</v>
+        <v>0.822</v>
       </c>
       <c r="H6" t="n">
         <v>48.2</v>
       </c>
       <c r="I6" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J6" t="n">
-        <v>78.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K6" t="n">
         <v>0.469</v>
       </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M6" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.391</v>
+        <v>0.389</v>
       </c>
       <c r="O6" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P6" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="R6" t="n">
         <v>10.7</v>
@@ -1437,13 +1504,13 @@
         <v>31.3</v>
       </c>
       <c r="T6" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U6" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V6" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="W6" t="n">
         <v>7.5</v>
@@ -1452,22 +1519,22 @@
         <v>5.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="n">
         <v>20.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.5</v>
+        <v>100.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1482,7 +1549,7 @@
         <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AJ6" t="n">
         <v>25</v>
@@ -1500,16 +1567,16 @@
         <v>2</v>
       </c>
       <c r="AO6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP6" t="n">
         <v>14</v>
       </c>
       <c r="AQ6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AS6" t="n">
         <v>8</v>
@@ -1518,25 +1585,25 @@
         <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AW6" t="n">
         <v>9</v>
       </c>
       <c r="AX6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY6" t="n">
         <v>4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB6" t="n">
         <v>12</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-30-2008-09</t>
+          <t>2009-03-30</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>1.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE7" t="n">
         <v>11</v>
@@ -1661,7 +1728,7 @@
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI7" t="n">
         <v>8</v>
@@ -1694,7 +1761,7 @@
         <v>13</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
         <v>5</v>
@@ -1706,10 +1773,10 @@
         <v>8</v>
       </c>
       <c r="AW7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY7" t="n">
         <v>8</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-30-2008-09</t>
+          <t>2009-03-30</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>3.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1894,7 +1961,7 @@
         <v>2</v>
       </c>
       <c r="AY8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ8" t="n">
         <v>26</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-30-2008-09</t>
+          <t>2009-03-30</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-0.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE9" t="n">
         <v>16</v>
@@ -2025,13 +2092,13 @@
         <v>16</v>
       </c>
       <c r="AH9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI9" t="n">
         <v>22</v>
       </c>
       <c r="AJ9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK9" t="n">
         <v>18</v>
@@ -2061,7 +2128,7 @@
         <v>18</v>
       </c>
       <c r="AT9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU9" t="n">
         <v>16</v>
@@ -2073,10 +2140,10 @@
         <v>29</v>
       </c>
       <c r="AX9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ9" t="n">
         <v>18</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-30-2008-09</t>
+          <t>2009-03-30</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E10" t="n">
         <v>25</v>
       </c>
       <c r="F10" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G10" t="n">
-        <v>0.338</v>
+        <v>0.342</v>
       </c>
       <c r="H10" t="n">
         <v>48.5</v>
@@ -2135,7 +2202,7 @@
         <v>39.5</v>
       </c>
       <c r="J10" t="n">
-        <v>86.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="K10" t="n">
         <v>0.459</v>
@@ -2144,31 +2211,31 @@
         <v>6.7</v>
       </c>
       <c r="M10" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="N10" t="n">
         <v>0.373</v>
       </c>
       <c r="O10" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="P10" t="n">
-        <v>29</v>
+        <v>29.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.789</v>
+        <v>0.787</v>
       </c>
       <c r="R10" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S10" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="T10" t="n">
         <v>41.9</v>
       </c>
       <c r="U10" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="V10" t="n">
         <v>14.9</v>
@@ -2183,7 +2250,7 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AA10" t="n">
         <v>23.4</v>
@@ -2195,7 +2262,7 @@
         <v>-3.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2216,7 +2283,7 @@
         <v>3</v>
       </c>
       <c r="AK10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL10" t="n">
         <v>16</v>
@@ -2234,7 +2301,7 @@
         <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR10" t="n">
         <v>9</v>
@@ -2246,7 +2313,7 @@
         <v>11</v>
       </c>
       <c r="AU10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV10" t="n">
         <v>23</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-30-2008-09</t>
+          <t>2009-03-30</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>3.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE11" t="n">
         <v>5</v>
@@ -2389,7 +2456,7 @@
         <v>6</v>
       </c>
       <c r="AH11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI11" t="n">
         <v>26</v>
@@ -2410,7 +2477,7 @@
         <v>11</v>
       </c>
       <c r="AO11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP11" t="n">
         <v>20</v>
@@ -2428,7 +2495,7 @@
         <v>4</v>
       </c>
       <c r="AU11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV11" t="n">
         <v>15</v>
@@ -2446,10 +2513,10 @@
         <v>2</v>
       </c>
       <c r="BA11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC11" t="n">
         <v>6</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-30-2008-09</t>
+          <t>2009-03-30</t>
         </is>
       </c>
     </row>
@@ -2559,19 +2626,19 @@
         <v>-1.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI12" t="n">
         <v>4</v>
@@ -2583,13 +2650,13 @@
         <v>21</v>
       </c>
       <c r="AL12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM12" t="n">
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO12" t="n">
         <v>22</v>
@@ -2622,13 +2689,13 @@
         <v>10</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ12" t="n">
         <v>28</v>
       </c>
       <c r="BA12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB12" t="n">
         <v>5</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-30-2008-09</t>
+          <t>2009-03-30</t>
         </is>
       </c>
     </row>
@@ -2741,10 +2808,10 @@
         <v>-8.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF13" t="n">
         <v>28</v>
@@ -2792,10 +2859,10 @@
         <v>26</v>
       </c>
       <c r="AU13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW13" t="n">
         <v>24</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-30-2008-09</t>
+          <t>2009-03-30</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E14" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F14" t="n">
         <v>15</v>
       </c>
       <c r="G14" t="n">
-        <v>0.792</v>
+        <v>0.795</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>40.6</v>
+        <v>40.5</v>
       </c>
       <c r="J14" t="n">
-        <v>85.2</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K14" t="n">
         <v>0.476</v>
@@ -2872,31 +2939,31 @@
         <v>6.8</v>
       </c>
       <c r="M14" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="N14" t="n">
-        <v>0.362</v>
+        <v>0.365</v>
       </c>
       <c r="O14" t="n">
         <v>19.6</v>
       </c>
       <c r="P14" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="Q14" t="n">
         <v>0.768</v>
       </c>
       <c r="R14" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="S14" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T14" t="n">
         <v>44.1</v>
       </c>
       <c r="U14" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="V14" t="n">
         <v>13.6</v>
@@ -2914,16 +2981,16 @@
         <v>20.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.6</v>
+        <v>107.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2944,7 +3011,7 @@
         <v>4</v>
       </c>
       <c r="AK14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL14" t="n">
         <v>13</v>
@@ -2956,19 +3023,19 @@
         <v>17</v>
       </c>
       <c r="AO14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP14" t="n">
         <v>11</v>
       </c>
-      <c r="AP14" t="n">
-        <v>9</v>
-      </c>
       <c r="AQ14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR14" t="n">
         <v>3</v>
       </c>
       <c r="AS14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2986,10 +3053,10 @@
         <v>9</v>
       </c>
       <c r="AY14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA14" t="n">
         <v>8</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-30-2008-09</t>
+          <t>2009-03-30</t>
         </is>
       </c>
     </row>
@@ -3027,22 +3094,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F15" t="n">
         <v>54</v>
       </c>
       <c r="G15" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
       </c>
       <c r="I15" t="n">
-        <v>34.8</v>
+        <v>34.7</v>
       </c>
       <c r="J15" t="n">
         <v>77.3</v>
@@ -3057,13 +3124,13 @@
         <v>13.2</v>
       </c>
       <c r="N15" t="n">
-        <v>0.347</v>
+        <v>0.349</v>
       </c>
       <c r="O15" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="P15" t="n">
-        <v>25.3</v>
+        <v>25.1</v>
       </c>
       <c r="Q15" t="n">
         <v>0.756</v>
@@ -3072,16 +3139,16 @@
         <v>10.5</v>
       </c>
       <c r="S15" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="T15" t="n">
-        <v>38.8</v>
+        <v>38.7</v>
       </c>
       <c r="U15" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="V15" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W15" t="n">
         <v>7.4</v>
@@ -3093,19 +3160,19 @@
         <v>5.5</v>
       </c>
       <c r="Z15" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="AA15" t="n">
         <v>21.7</v>
       </c>
-      <c r="AA15" t="n">
-        <v>21.8</v>
-      </c>
       <c r="AB15" t="n">
-        <v>93.3</v>
+        <v>93</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.2</v>
+        <v>-6.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3135,16 +3202,16 @@
         <v>27</v>
       </c>
       <c r="AN15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP15" t="n">
         <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR15" t="n">
         <v>22</v>
@@ -3153,7 +3220,7 @@
         <v>29</v>
       </c>
       <c r="AT15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AU15" t="n">
         <v>30</v>
@@ -3162,7 +3229,7 @@
         <v>24</v>
       </c>
       <c r="AW15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX15" t="n">
         <v>21</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-30-2008-09</t>
+          <t>2009-03-30</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E16" t="n">
         <v>39</v>
       </c>
       <c r="F16" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G16" t="n">
-        <v>0.527</v>
+        <v>0.534</v>
       </c>
       <c r="H16" t="n">
         <v>48.6</v>
@@ -3227,7 +3294,7 @@
         <v>37</v>
       </c>
       <c r="J16" t="n">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
       <c r="K16" t="n">
         <v>0.455</v>
@@ -3236,10 +3303,10 @@
         <v>6.8</v>
       </c>
       <c r="M16" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0.35</v>
+        <v>0.351</v>
       </c>
       <c r="O16" t="n">
         <v>17.4</v>
@@ -3248,13 +3315,13 @@
         <v>22.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.76</v>
+        <v>0.762</v>
       </c>
       <c r="R16" t="n">
         <v>10.2</v>
       </c>
       <c r="S16" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="T16" t="n">
         <v>39.3</v>
@@ -3272,7 +3339,7 @@
         <v>5.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z16" t="n">
         <v>20.7</v>
@@ -3281,19 +3348,19 @@
         <v>19.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>98.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
       </c>
       <c r="AF16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG16" t="n">
         <v>14</v>
@@ -3350,7 +3417,7 @@
         <v>5</v>
       </c>
       <c r="AY16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ16" t="n">
         <v>16</v>
@@ -3359,7 +3426,7 @@
         <v>25</v>
       </c>
       <c r="BB16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC16" t="n">
         <v>15</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-30-2008-09</t>
+          <t>2009-03-30</t>
         </is>
       </c>
     </row>
@@ -3394,13 +3461,13 @@
         <v>74</v>
       </c>
       <c r="E17" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F17" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G17" t="n">
-        <v>0.432</v>
+        <v>0.419</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3415,40 +3482,40 @@
         <v>0.443</v>
       </c>
       <c r="L17" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M17" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0.362</v>
+        <v>0.36</v>
       </c>
       <c r="O17" t="n">
         <v>20</v>
       </c>
       <c r="P17" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.781</v>
+        <v>0.782</v>
       </c>
       <c r="R17" t="n">
         <v>12.1</v>
       </c>
       <c r="S17" t="n">
-        <v>29.1</v>
+        <v>28.9</v>
       </c>
       <c r="T17" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="U17" t="n">
         <v>21.4</v>
       </c>
       <c r="V17" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W17" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X17" t="n">
         <v>3.8</v>
@@ -3457,19 +3524,19 @@
         <v>4.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="AA17" t="n">
         <v>22.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>99</v>
+        <v>98.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>-1</v>
+        <v>-1.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE17" t="n">
         <v>19</v>
@@ -3484,7 +3551,7 @@
         <v>22</v>
       </c>
       <c r="AI17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ17" t="n">
         <v>8</v>
@@ -3499,13 +3566,13 @@
         <v>20</v>
       </c>
       <c r="AN17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO17" t="n">
         <v>7</v>
       </c>
       <c r="AP17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ17" t="n">
         <v>11</v>
@@ -3514,10 +3581,10 @@
         <v>5</v>
       </c>
       <c r="AS17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AT17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AU17" t="n">
         <v>10</v>
@@ -3526,13 +3593,13 @@
         <v>13</v>
       </c>
       <c r="AW17" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
       </c>
       <c r="AY17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ17" t="n">
         <v>30</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-30-2008-09</t>
+          <t>2009-03-30</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-4.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
@@ -3663,10 +3730,10 @@
         <v>25</v>
       </c>
       <c r="AH18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI18" t="n">
         <v>18</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>19</v>
       </c>
       <c r="AJ18" t="n">
         <v>7</v>
@@ -3684,13 +3751,13 @@
         <v>22</v>
       </c>
       <c r="AO18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ18" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AR18" t="n">
         <v>7</v>
@@ -3705,7 +3772,7 @@
         <v>20</v>
       </c>
       <c r="AV18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW18" t="n">
         <v>27</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-30-2008-09</t>
+          <t>2009-03-30</t>
         </is>
       </c>
     </row>
@@ -3755,28 +3822,28 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E19" t="n">
         <v>30</v>
       </c>
       <c r="F19" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G19" t="n">
-        <v>0.405</v>
+        <v>0.411</v>
       </c>
       <c r="H19" t="n">
         <v>48.4</v>
       </c>
       <c r="I19" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="J19" t="n">
-        <v>79.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="K19" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L19" t="n">
         <v>7.9</v>
@@ -3785,22 +3852,22 @@
         <v>21</v>
       </c>
       <c r="N19" t="n">
-        <v>0.376</v>
+        <v>0.378</v>
       </c>
       <c r="O19" t="n">
         <v>18.9</v>
       </c>
       <c r="P19" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.777</v>
+        <v>0.779</v>
       </c>
       <c r="R19" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S19" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="T19" t="n">
         <v>39.8</v>
@@ -3827,46 +3894,46 @@
         <v>20.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>98.40000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.8</v>
+        <v>-2.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AE19" t="n">
         <v>21</v>
       </c>
       <c r="AF19" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG19" t="n">
         <v>21</v>
       </c>
       <c r="AH19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI19" t="n">
         <v>27</v>
       </c>
       <c r="AJ19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK19" t="n">
         <v>24</v>
       </c>
       <c r="AL19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AM19" t="n">
         <v>4</v>
       </c>
       <c r="AN19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP19" t="n">
         <v>18</v>
@@ -3884,7 +3951,7 @@
         <v>25</v>
       </c>
       <c r="AU19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV19" t="n">
         <v>9</v>
@@ -3896,7 +3963,7 @@
         <v>17</v>
       </c>
       <c r="AY19" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ19" t="n">
         <v>25</v>
@@ -3905,10 +3972,10 @@
         <v>18</v>
       </c>
       <c r="BB19" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BC19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-30-2008-09</t>
+          <t>2009-03-30</t>
         </is>
       </c>
     </row>
@@ -4018,13 +4085,13 @@
         <v>25</v>
       </c>
       <c r="AE20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG20" t="n">
         <v>9</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>10</v>
       </c>
       <c r="AH20" t="n">
         <v>28</v>
@@ -4057,7 +4124,7 @@
         <v>3</v>
       </c>
       <c r="AR20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS20" t="n">
         <v>16</v>
@@ -4069,10 +4136,10 @@
         <v>28</v>
       </c>
       <c r="AV20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX20" t="n">
         <v>23</v>
@@ -4084,7 +4151,7 @@
         <v>9</v>
       </c>
       <c r="BA20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB20" t="n">
         <v>25</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-30-2008-09</t>
+          <t>2009-03-30</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E21" t="n">
         <v>29</v>
       </c>
       <c r="F21" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G21" t="n">
-        <v>0.392</v>
+        <v>0.397</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
@@ -4137,37 +4204,37 @@
         <v>38.5</v>
       </c>
       <c r="J21" t="n">
-        <v>86.5</v>
+        <v>86.7</v>
       </c>
       <c r="K21" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L21" t="n">
         <v>10.2</v>
       </c>
       <c r="M21" t="n">
-        <v>28.3</v>
+        <v>28.4</v>
       </c>
       <c r="N21" t="n">
         <v>0.361</v>
       </c>
       <c r="O21" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="P21" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.787</v>
+        <v>0.788</v>
       </c>
       <c r="R21" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S21" t="n">
         <v>31.1</v>
       </c>
       <c r="T21" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="U21" t="n">
         <v>21.2</v>
@@ -4176,28 +4243,28 @@
         <v>14.5</v>
       </c>
       <c r="W21" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X21" t="n">
         <v>2.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z21" t="n">
         <v>20.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AB21" t="n">
         <v>105.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.7</v>
+        <v>-2.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AE21" t="n">
         <v>22</v>
@@ -4209,10 +4276,10 @@
         <v>22</v>
       </c>
       <c r="AH21" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AI21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ21" t="n">
         <v>1</v>
@@ -4227,16 +4294,16 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO21" t="n">
         <v>21</v>
       </c>
       <c r="AP21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR21" t="n">
         <v>15</v>
@@ -4254,7 +4321,7 @@
         <v>18</v>
       </c>
       <c r="AW21" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4272,7 +4339,7 @@
         <v>4</v>
       </c>
       <c r="BC21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-30-2008-09</t>
+          <t>2009-03-30</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>-5.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE22" t="n">
         <v>26</v>
@@ -4391,7 +4458,7 @@
         <v>26</v>
       </c>
       <c r="AH22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI22" t="n">
         <v>17</v>
@@ -4436,7 +4503,7 @@
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX22" t="n">
         <v>22</v>
@@ -4445,7 +4512,7 @@
         <v>17</v>
       </c>
       <c r="AZ22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA22" t="n">
         <v>19</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-30-2008-09</t>
+          <t>2009-03-30</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E23" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F23" t="n">
         <v>18</v>
       </c>
       <c r="G23" t="n">
-        <v>0.753</v>
+        <v>0.75</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
@@ -4501,19 +4568,19 @@
         <v>36</v>
       </c>
       <c r="J23" t="n">
-        <v>78.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="K23" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="L23" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="M23" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0.388</v>
+        <v>0.387</v>
       </c>
       <c r="O23" t="n">
         <v>19.9</v>
@@ -4525,10 +4592,10 @@
         <v>0.721</v>
       </c>
       <c r="R23" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="S23" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="T23" t="n">
         <v>43.3</v>
@@ -4537,13 +4604,13 @@
         <v>19.5</v>
       </c>
       <c r="V23" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W23" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X23" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y23" t="n">
         <v>3.7</v>
@@ -4552,7 +4619,7 @@
         <v>20.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="AB23" t="n">
         <v>102.2</v>
@@ -4561,10 +4628,10 @@
         <v>7.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AE23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF23" t="n">
         <v>3</v>
@@ -4573,7 +4640,7 @@
         <v>3</v>
       </c>
       <c r="AH23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI23" t="n">
         <v>25</v>
@@ -4603,7 +4670,7 @@
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS23" t="n">
         <v>1</v>
@@ -4615,13 +4682,13 @@
         <v>29</v>
       </c>
       <c r="AV23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY23" t="n">
         <v>2</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-30-2008-09</t>
+          <t>2009-03-30</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4816,7 @@
         <v>15</v>
       </c>
       <c r="AF24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG24" t="n">
         <v>15</v>
@@ -4758,13 +4825,13 @@
         <v>25</v>
       </c>
       <c r="AI24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ24" t="n">
         <v>17</v>
       </c>
       <c r="AK24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL24" t="n">
         <v>29</v>
@@ -4776,7 +4843,7 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP24" t="n">
         <v>6</v>
@@ -4788,16 +4855,16 @@
         <v>2</v>
       </c>
       <c r="AS24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT24" t="n">
         <v>13</v>
       </c>
       <c r="AU24" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AV24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW24" t="n">
         <v>4</v>
@@ -4806,10 +4873,10 @@
         <v>11</v>
       </c>
       <c r="AY24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-30-2008-09</t>
+          <t>2009-03-30</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>1.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
@@ -4982,7 +5049,7 @@
         <v>29</v>
       </c>
       <c r="AW25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX25" t="n">
         <v>12</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-30-2008-09</t>
+          <t>2009-03-30</t>
         </is>
       </c>
     </row>
@@ -5029,28 +5096,28 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E26" t="n">
         <v>46</v>
       </c>
       <c r="F26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G26" t="n">
-        <v>0.639</v>
+        <v>0.63</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J26" t="n">
-        <v>79.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.463</v>
+        <v>0.461</v>
       </c>
       <c r="L26" t="n">
         <v>7.2</v>
@@ -5059,28 +5126,28 @@
         <v>19.1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.378</v>
+        <v>0.379</v>
       </c>
       <c r="O26" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P26" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.77</v>
+        <v>0.768</v>
       </c>
       <c r="R26" t="n">
         <v>13</v>
       </c>
       <c r="S26" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="T26" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="U26" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V26" t="n">
         <v>12.8</v>
@@ -5092,28 +5159,28 @@
         <v>4.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA26" t="n">
         <v>21.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.40000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AE26" t="n">
         <v>8</v>
       </c>
       <c r="AF26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG26" t="n">
         <v>8</v>
@@ -5134,16 +5201,16 @@
         <v>9</v>
       </c>
       <c r="AM26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN26" t="n">
         <v>7</v>
       </c>
       <c r="AO26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP26" t="n">
         <v>17</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>16</v>
       </c>
       <c r="AQ26" t="n">
         <v>15</v>
@@ -5161,7 +5228,7 @@
         <v>22</v>
       </c>
       <c r="AV26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW26" t="n">
         <v>26</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-30-2008-09</t>
+          <t>2009-03-30</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5383,7 @@
         <v>11</v>
       </c>
       <c r="AM27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN27" t="n">
         <v>18</v>
@@ -5337,13 +5404,13 @@
         <v>27</v>
       </c>
       <c r="AT27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AU27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AV27" t="n">
         <v>26</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>27</v>
       </c>
       <c r="AW27" t="n">
         <v>18</v>
@@ -5352,7 +5419,7 @@
         <v>27</v>
       </c>
       <c r="AY27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-30-2008-09</t>
+          <t>2009-03-30</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>3.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5483,7 +5550,7 @@
         <v>5</v>
       </c>
       <c r="AH28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI28" t="n">
         <v>11</v>
@@ -5519,7 +5586,7 @@
         <v>4</v>
       </c>
       <c r="AT28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU28" t="n">
         <v>8</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-30-2008-09</t>
+          <t>2009-03-30</t>
         </is>
       </c>
     </row>
@@ -5653,22 +5720,22 @@
         <v>-2.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE29" t="n">
         <v>23</v>
       </c>
       <c r="AF29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG29" t="n">
         <v>23</v>
       </c>
       <c r="AH29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ29" t="n">
         <v>16</v>
@@ -5686,7 +5753,7 @@
         <v>10</v>
       </c>
       <c r="AO29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP29" t="n">
         <v>24</v>
@@ -5725,7 +5792,7 @@
         <v>23</v>
       </c>
       <c r="BB29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC29" t="n">
         <v>23</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-30-2008-09</t>
+          <t>2009-03-30</t>
         </is>
       </c>
     </row>
@@ -5757,28 +5824,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E30" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F30" t="n">
         <v>27</v>
       </c>
       <c r="G30" t="n">
-        <v>0.63</v>
+        <v>0.625</v>
       </c>
       <c r="H30" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I30" t="n">
         <v>38.5</v>
       </c>
       <c r="J30" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.477</v>
+        <v>0.476</v>
       </c>
       <c r="L30" t="n">
         <v>4.8</v>
@@ -5787,7 +5854,7 @@
         <v>13.8</v>
       </c>
       <c r="N30" t="n">
-        <v>0.349</v>
+        <v>0.347</v>
       </c>
       <c r="O30" t="n">
         <v>21.5</v>
@@ -5799,16 +5866,16 @@
         <v>0.77</v>
       </c>
       <c r="R30" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S30" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T30" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U30" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="V30" t="n">
         <v>14.9</v>
@@ -5817,46 +5884,46 @@
         <v>8.699999999999999</v>
       </c>
       <c r="X30" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y30" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AA30" t="n">
         <v>23.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>103.4</v>
+        <v>103.3</v>
       </c>
       <c r="AC30" t="n">
         <v>3.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AE30" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF30" t="n">
         <v>8</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>9</v>
       </c>
       <c r="AG30" t="n">
         <v>9</v>
       </c>
       <c r="AH30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ30" t="n">
         <v>15</v>
       </c>
       <c r="AK30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL30" t="n">
         <v>26</v>
@@ -5865,7 +5932,7 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
@@ -5874,7 +5941,7 @@
         <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR30" t="n">
         <v>10</v>
@@ -5898,7 +5965,7 @@
         <v>15</v>
       </c>
       <c r="AY30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ30" t="n">
         <v>23</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-30-2008-09</t>
+          <t>2009-03-30</t>
         </is>
       </c>
     </row>
@@ -6053,7 +6120,7 @@
         <v>25</v>
       </c>
       <c r="AP31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ31" t="n">
         <v>18</v>
@@ -6074,7 +6141,7 @@
         <v>12</v>
       </c>
       <c r="AW31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX31" t="n">
         <v>24</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-30-2008-09</t>
+          <t>2009-03-30</t>
         </is>
       </c>
     </row>
